--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321489</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321487</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R2" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>98287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R3" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>98293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R2" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B3" t="n">
-        <v>98287</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R3" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321489</v>
       </c>
       <c r="B2" t="n">
-        <v>98296</v>
+        <v>98313</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>123321487</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B2" t="n">
-        <v>98313</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R2" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>98419</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R3" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>98421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R2" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B3" t="n">
-        <v>98419</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R3" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R2" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R3" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321487</v>
+        <v>123321489</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601506</v>
+        <v>601451</v>
       </c>
       <c r="R2" t="n">
-        <v>6802037</v>
+        <v>6801978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>2024_463</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:27</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B3" t="n">
-        <v>97996</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R3" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321489</v>
+        <v>123321487</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601451</v>
+        <v>601506</v>
       </c>
       <c r="R2" t="n">
-        <v>6801978</v>
+        <v>6802037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_463</t>
+          <t>2024_465</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:14</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>i kant på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,59 +805,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321487</v>
+        <v>130670079</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödmyran, Hls</t>
+          <t>Kungsgården, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601506</v>
+        <v>601490</v>
       </c>
       <c r="R3" t="n">
-        <v>6802037</v>
+        <v>6802427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,32 +879,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_465</t>
+          <t>195</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>07:27</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>07:27</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i kant på myr</t>
+          <t>Spillning på väg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +909,260 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130670080</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kungsgården, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601334</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6802073</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123321489</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rödmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601451</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6801978</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_463</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Felix Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 67300-2021 artfynd.xlsx
+++ b/artfynd/A 67300-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321487</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130670079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130670080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,8 +1187,19 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321489</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>